--- a/output/pdf_financials_xlsx/PYR.xlsx
+++ b/output/pdf_financials_xlsx/PYR.xlsx
@@ -5498,19 +5498,19 @@
         <v>0.711035</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.66309</v>
+        <v>3.161038</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.325386</v>
+        <v>4.104385</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.628305</v>
+        <v>5.297409</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>5.313555</v>
+        <v>6.047559</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>5.67958</v>
+        <v>6.580791</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>6.147638</v>
@@ -21013,7 +21013,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -22259,7 +22263,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -23343,7 +23351,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -24684,7 +24696,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PYR.xlsx
+++ b/output/pdf_financials_xlsx/PYR.xlsx
@@ -2427,46 +2427,46 @@
         <v>0.7229409999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.237291</v>
+        <v>0.481396</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.195571</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.182835</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.362183</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.7673680000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.385257</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.622846</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.644981</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.034431</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.445649</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.802616</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.975461</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.088707</v>
       </c>
     </row>
     <row r="35">
@@ -2531,46 +2531,46 @@
         <v>0.7229409999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.237291</v>
+        <v>0.481396</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.195571</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.182835</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.362183</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.7673680000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.385257</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.622846</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.644981</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.034431</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.445649</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.802616</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.975461</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.088707</v>
       </c>
     </row>
     <row r="37">
@@ -3155,46 +3155,46 @@
         <v>4.072689</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.397995</v>
+        <v>3.15389</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.676525</v>
+        <v>0.480954</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.04501</v>
+        <v>0.862175</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.193446</v>
+        <v>2.831263</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.12702</v>
+        <v>1.359652</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.968963</v>
+        <v>1.583706</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.251443</v>
+        <v>1.628597</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.86828</v>
+        <v>2.223299</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.324554</v>
+        <v>1.290123</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>38.758984</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.94714</v>
+        <v>3.501491</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.632447</v>
+        <v>3.829831</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.183976</v>
+        <v>4.208515</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.211692</v>
+        <v>3.122985</v>
       </c>
     </row>
     <row r="49">
@@ -7142,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0.09625</v>
+        <v>0.161488</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.09625</v>
+        <v>0.161488</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/PYR.xlsx
+++ b/output/pdf_financials_xlsx/PYR.xlsx
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.40437</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.550742</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>-0</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-39.171899</v>
+        <v>-38.767529</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-32.091043</v>
+        <v>-31.540301</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-28.725921</v>
@@ -2116,13 +2116,13 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.163727</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.127405</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.111937</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.9265139999999999</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.239722</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.9025919999999999</v>
+        <v>2.204132</v>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
@@ -2180,13 +2180,13 @@
         <v>-3.27861</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.917779</v>
+        <v>-4.754052</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.952219</v>
+        <v>-6.824814</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.174303</v>
+        <v>-6.062366</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-39.171899</v>
+        <v>-37.841015</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-32.091043</v>
+        <v>-30.300579</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-27.823329</v>
+        <v>-26.521789</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         <v>-195.6116679325164</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-78.78527133037264</v>
+        <v>-76.16228316455471</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-133.1298724103733</v>
+        <v>-130.6901605148701</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-85.8393204039394</v>
+        <v>-84.28309680946148</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-315.0940679519661</v>
+        <v>-304.3885963195547</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-168.7802768379925</v>
+        <v>-159.3634744739041</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-225.3798820761079</v>
+        <v>-214.8368973844724</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -5882,13 +5882,13 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.163727</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.127405</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.111937</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -5897,19 +5897,19 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.9265139999999999</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.239722</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>2.204132</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.269472</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.318866</v>
       </c>
     </row>
     <row r="101">
@@ -29952,7 +29952,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -30035,7 +30039,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -31069,7 +31077,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -33417,7 +33429,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -43325,7 +43337,11 @@
           <t>Depreciation on property plant and equipment [note 9]</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -61553,7 +61569,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PYR.xlsx
+++ b/output/pdf_financials_xlsx/PYR.xlsx
@@ -2754,31 +2754,31 @@
         <v>0.222151</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.060138</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.043677</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.06732100000000001</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.270536</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.24056</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.842715</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.31081</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.310824</v>
       </c>
     </row>
     <row r="41">
@@ -2806,31 +2806,31 @@
         <v>0.222151</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.060138</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.043677</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.06732100000000001</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.270536</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>18.624631</v>
+        <v>18.865191</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>9.265665</v>
+        <v>10.10838</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>9.624611</v>
+        <v>9.935421</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.147739</v>
+        <v>4.458563</v>
       </c>
     </row>
     <row r="42">
@@ -3170,31 +3170,31 @@
         <v>1.359652</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.583706</v>
+        <v>1.523568</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.628597</v>
+        <v>1.58492</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.223299</v>
+        <v>2.155978</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>1.290123</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>38.758984</v>
+        <v>38.488448</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.501491</v>
+        <v>3.260931</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.829831</v>
+        <v>2.987116</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.208515</v>
+        <v>3.897705</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.122985</v>
+        <v>2.812161</v>
       </c>
     </row>
     <row r="49">
@@ -4032,31 +4032,31 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.734785</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.747325</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.072257</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.780628</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>5.457259</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>6.065996</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>4.850681</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>7.450691</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>6.224169</v>
       </c>
     </row>
     <row r="65">
@@ -4170,49 +4170,49 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.462501</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.77697</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.811276</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.525555</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.666021</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.625818</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.545018</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>1.295628</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.080128</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.866823</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>3.730048</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>2.891053</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.897663</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>4.028906</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>3.513815</v>
       </c>
     </row>
     <row r="68">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-4.064183</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-1.245759</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0</v>
@@ -6270,10 +6270,10 @@
         <v>3.11304</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>2.112005</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.68535</v>
       </c>
     </row>
     <row r="108">
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -29865,7 +29865,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -44150,7 +44154,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -46235,7 +46243,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -51352,7 +51364,11 @@
           <t>Net change in non-cash operating working capital total</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E489" s="5" t="n">
         <v>-4.064183</v>
       </c>
